--- a/result/pc64/FutSquads/66/cards_ng_db_1.db_Changelogs/KitsChangelog.xlsx
+++ b/result/pc64/FutSquads/66/cards_ng_db_1.db_Changelogs/KitsChangelog.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Added" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Removed" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Modified" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Added" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modified" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Added'!$A$1:$H$25</definedName>
@@ -1774,7 +1774,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>131159</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
@@ -1793,19 +1793,19 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>teamtechid</t>
+          <t>armbandtype, jerseybacknameplacementcode, jerseycollargeometrytype, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimpercent, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolorsecpercent, teamcolorsecr, teamcolortertb, teamcolortertg, teamcolortertpercent, teamcolortertr, teamtechid</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>113154</t>
+          <t>132585</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
@@ -1824,19 +1824,19 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>16946</t>
+          <t>16922</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>teamtechid</t>
+          <t>captainarmband, jerseybacknameplacementcode, jerseycollargeometrytype, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynameoutlinewidth, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, jerseyrightsleevebadge, numberfonttype, powid, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamtechid</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>131271</t>
+          <t>115891</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>17361</t>
+          <t>17163</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -1898,7 +1898,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>113155</t>
+          <t>113154</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr"/>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16947</t>
+          <t>16946</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1929,7 +1929,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>132483</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr"/>
@@ -1948,19 +1948,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>16928</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolorsecr, teamcolortertb, teamcolortertg, teamcolortertr, teamtechid</t>
+          <t>jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamtechid</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>132482</t>
+          <t>113155</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr"/>
@@ -1979,19 +1979,19 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>16923</t>
+          <t>16947</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamtechid</t>
+          <t>teamtechid</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>131271</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
@@ -2010,19 +2010,19 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>armbandtype, jerseybacknameplacementcode, jerseycollargeometrytype, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimpercent, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolorsecpercent, teamcolorsecr, teamcolortertb, teamcolortertg, teamcolortertpercent, teamcolortertr, teamtechid</t>
+          <t>teamtechid</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>132483</t>
+          <t>132482</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>16923</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
@@ -2053,7 +2053,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>115891</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
@@ -2072,19 +2072,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>17163</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>teamtechid</t>
+          <t>jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolorsecr, teamcolortertb, teamcolortertg, teamcolortertr, teamtechid</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>132585</t>
+          <t>131159</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
@@ -2103,19 +2103,19 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>captainarmband, jerseybacknameplacementcode, jerseycollargeometrytype, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynameoutlinewidth, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, jerseyrightsleevebadge, numberfonttype, powid, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamtechid</t>
+          <t>teamtechid</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>132483</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
@@ -2134,19 +2134,19 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>16937</t>
+          <t>16927</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>armbandtype, jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolorsecr, teamcolortertb, teamcolortertg, teamcolortertr, teamkittypetechid, teamtechid</t>
+          <t>armbandtype, jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamkittypetechid, teamtechid</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
@@ -2165,7 +2165,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>16934</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>132482</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
@@ -2196,19 +2196,19 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>16924</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>armbandtype, jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamkittypetechid, teamtechid</t>
+          <t>armbandtype, jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolorsecr, teamcolortertb, teamcolortertg, teamcolortertr, teamkittypetechid, teamtechid</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>132483</t>
+          <t>16075</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
@@ -2227,19 +2227,19 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>16927</t>
+          <t>16920</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>armbandtype, jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamkittypetechid, teamtechid</t>
+          <t>jerseybacknameplacementcode, jerseycollargeometrytype, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolortertb, teamcolortertg, teamcolortertr, teamkittypetechid, teamtechid</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>132482</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
@@ -2258,19 +2258,19 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16920</t>
+          <t>16924</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>jerseybacknameplacementcode, jerseycollargeometrytype, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolortertb, teamcolortertg, teamcolortertr, teamkittypetechid, teamtechid</t>
+          <t>armbandtype, jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamkittypetechid, teamtechid</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>16935</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -2363,7 +2363,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>132483</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
@@ -2382,19 +2382,19 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>16938</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolorsecr, teamcolortertb, teamcolortertg, teamcolortertr, teamkittypetechid, teamtechid</t>
+          <t>armbandtype, jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamkittypetechid, teamtechid</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>132483</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>16926</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>armbandtype, jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamkittypetechid, teamtechid</t>
+          <t>jerseybacknameplacementcode, jerseynamecolorb, jerseynamecolorg, jerseynamecolorr, jerseynamefonttype, jerseynameoutlinecolorb, jerseynameoutlinecolorg, jerseynameoutlinecolorr, jerseynumbercolorprimb, jerseynumbercolorprimg, jerseynumbercolorprimr, jerseynumbercolorsecb, jerseynumbercolorsecg, jerseynumbercolorsecr, jerseynumbercolorterb, jerseynumbercolorterg, jerseynumbercolorterr, numberfonttype, shortsnumbercolorprimb, shortsnumbercolorprimg, shortsnumbercolorprimr, shortsnumbercolorsecb, shortsnumbercolorsecg, shortsnumbercolorsecr, shortsnumbercolorterb, shortsnumbercolorterg, shortsnumbercolorterr, shortsnumberfonttype, shortsnumberplacementcode, teamcolorprimb, teamcolorprimg, teamcolorprimr, teamcolorsecb, teamcolorsecg, teamcolorsecr, teamcolortertb, teamcolortertg, teamcolortertr, teamkittypetechid, teamtechid</t>
         </is>
       </c>
     </row>
